--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.53316690910771</v>
+        <v>2.361639622730002</v>
       </c>
       <c r="D2" t="n">
-        <v>14.81919758291646</v>
+        <v>2.408119607223925</v>
       </c>
       <c r="E2" t="n">
-        <v>14.10309980053095</v>
+        <v>2.291753717586279</v>
       </c>
       <c r="F2" t="n">
-        <v>13.81661177922605</v>
+        <v>2.245199414124233</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>4.972713737606329</v>
+        <v>0.8080659823610284</v>
       </c>
       <c r="D3" t="n">
-        <v>5.309401036149263</v>
+        <v>0.8627776683742553</v>
       </c>
       <c r="E3" t="n">
-        <v>14.10309980053095</v>
+        <v>2.291753717586279</v>
       </c>
       <c r="F3" t="n">
-        <v>13.81661177922605</v>
+        <v>2.245199414124233</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.90781293723779</v>
+        <v>6.32251960230114</v>
       </c>
       <c r="D4" t="n">
-        <v>38.68118619679159</v>
+        <v>6.285692756978633</v>
       </c>
       <c r="E4" t="n">
-        <v>14.10309980053095</v>
+        <v>2.291753717586279</v>
       </c>
       <c r="F4" t="n">
-        <v>13.81661177922605</v>
+        <v>2.245199414124233</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.6653366683312</v>
+        <v>5.63311720860382</v>
       </c>
       <c r="D5" t="n">
-        <v>34.30454068288012</v>
+        <v>5.574487860968019</v>
       </c>
       <c r="E5" t="n">
-        <v>14.10309980053095</v>
+        <v>2.291753717586279</v>
       </c>
       <c r="F5" t="n">
-        <v>13.81661177922605</v>
+        <v>2.245199414124233</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.43179997279722</v>
+        <v>6.407667495579548</v>
       </c>
       <c r="D6" t="n">
-        <v>39.13848266465259</v>
+        <v>6.360003433006045</v>
       </c>
       <c r="E6" t="n">
-        <v>14.10309980053095</v>
+        <v>2.291753717586279</v>
       </c>
       <c r="F6" t="n">
-        <v>13.81661177922605</v>
+        <v>2.245199414124233</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
